--- a/Backend/ac_shunt/reports/templates/roc_ac_shunt.xlsx
+++ b/Backend/ac_shunt/reports/templates/roc_ac_shunt.xlsx
@@ -2144,441 +2144,441 @@
     <col width="1.6328125" customWidth="1" style="36" min="255" max="305"/>
     <col width="2.453125" customWidth="1" style="36" min="306" max="306"/>
     <col width="3.36328125" customWidth="1" style="36" min="307" max="307"/>
-    <col hidden="1" style="36" min="308" max="309"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="308" max="309"/>
     <col width="3.453125" customWidth="1" style="36" min="310" max="310"/>
     <col width="1.6328125" customWidth="1" style="36" min="311" max="311"/>
     <col width="9.08984375" customWidth="1" style="36" min="312" max="510"/>
     <col width="1.6328125" customWidth="1" style="36" min="511" max="561"/>
     <col width="2.453125" customWidth="1" style="36" min="562" max="562"/>
     <col width="3.36328125" customWidth="1" style="36" min="563" max="563"/>
-    <col hidden="1" style="36" min="564" max="565"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="564" max="565"/>
     <col width="3.453125" customWidth="1" style="36" min="566" max="566"/>
     <col width="1.6328125" customWidth="1" style="36" min="567" max="567"/>
     <col width="9.08984375" customWidth="1" style="36" min="568" max="766"/>
     <col width="1.6328125" customWidth="1" style="36" min="767" max="817"/>
     <col width="2.453125" customWidth="1" style="36" min="818" max="818"/>
     <col width="3.36328125" customWidth="1" style="36" min="819" max="819"/>
-    <col hidden="1" style="36" min="820" max="821"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="820" max="821"/>
     <col width="3.453125" customWidth="1" style="36" min="822" max="822"/>
     <col width="1.6328125" customWidth="1" style="36" min="823" max="823"/>
     <col width="9.08984375" customWidth="1" style="36" min="824" max="1022"/>
     <col width="1.6328125" customWidth="1" style="36" min="1023" max="1073"/>
     <col width="2.453125" customWidth="1" style="36" min="1074" max="1074"/>
     <col width="3.36328125" customWidth="1" style="36" min="1075" max="1075"/>
-    <col hidden="1" style="36" min="1076" max="1077"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="1076" max="1077"/>
     <col width="3.453125" customWidth="1" style="36" min="1078" max="1078"/>
     <col width="1.6328125" customWidth="1" style="36" min="1079" max="1079"/>
     <col width="9.08984375" customWidth="1" style="36" min="1080" max="1278"/>
     <col width="1.6328125" customWidth="1" style="36" min="1279" max="1329"/>
     <col width="2.453125" customWidth="1" style="36" min="1330" max="1330"/>
     <col width="3.36328125" customWidth="1" style="36" min="1331" max="1331"/>
-    <col hidden="1" style="36" min="1332" max="1333"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="1332" max="1333"/>
     <col width="3.453125" customWidth="1" style="36" min="1334" max="1334"/>
     <col width="1.6328125" customWidth="1" style="36" min="1335" max="1335"/>
     <col width="9.08984375" customWidth="1" style="36" min="1336" max="1534"/>
     <col width="1.6328125" customWidth="1" style="36" min="1535" max="1585"/>
     <col width="2.453125" customWidth="1" style="36" min="1586" max="1586"/>
     <col width="3.36328125" customWidth="1" style="36" min="1587" max="1587"/>
-    <col hidden="1" style="36" min="1588" max="1589"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="1588" max="1589"/>
     <col width="3.453125" customWidth="1" style="36" min="1590" max="1590"/>
     <col width="1.6328125" customWidth="1" style="36" min="1591" max="1591"/>
     <col width="9.08984375" customWidth="1" style="36" min="1592" max="1790"/>
     <col width="1.6328125" customWidth="1" style="36" min="1791" max="1841"/>
     <col width="2.453125" customWidth="1" style="36" min="1842" max="1842"/>
     <col width="3.36328125" customWidth="1" style="36" min="1843" max="1843"/>
-    <col hidden="1" style="36" min="1844" max="1845"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="1844" max="1845"/>
     <col width="3.453125" customWidth="1" style="36" min="1846" max="1846"/>
     <col width="1.6328125" customWidth="1" style="36" min="1847" max="1847"/>
     <col width="9.08984375" customWidth="1" style="36" min="1848" max="2046"/>
     <col width="1.6328125" customWidth="1" style="36" min="2047" max="2097"/>
     <col width="2.453125" customWidth="1" style="36" min="2098" max="2098"/>
     <col width="3.36328125" customWidth="1" style="36" min="2099" max="2099"/>
-    <col hidden="1" style="36" min="2100" max="2101"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="2100" max="2101"/>
     <col width="3.453125" customWidth="1" style="36" min="2102" max="2102"/>
     <col width="1.6328125" customWidth="1" style="36" min="2103" max="2103"/>
     <col width="9.08984375" customWidth="1" style="36" min="2104" max="2302"/>
     <col width="1.6328125" customWidth="1" style="36" min="2303" max="2353"/>
     <col width="2.453125" customWidth="1" style="36" min="2354" max="2354"/>
     <col width="3.36328125" customWidth="1" style="36" min="2355" max="2355"/>
-    <col hidden="1" style="36" min="2356" max="2357"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="2356" max="2357"/>
     <col width="3.453125" customWidth="1" style="36" min="2358" max="2358"/>
     <col width="1.6328125" customWidth="1" style="36" min="2359" max="2359"/>
     <col width="9.08984375" customWidth="1" style="36" min="2360" max="2558"/>
     <col width="1.6328125" customWidth="1" style="36" min="2559" max="2609"/>
     <col width="2.453125" customWidth="1" style="36" min="2610" max="2610"/>
     <col width="3.36328125" customWidth="1" style="36" min="2611" max="2611"/>
-    <col hidden="1" style="36" min="2612" max="2613"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="2612" max="2613"/>
     <col width="3.453125" customWidth="1" style="36" min="2614" max="2614"/>
     <col width="1.6328125" customWidth="1" style="36" min="2615" max="2615"/>
     <col width="9.08984375" customWidth="1" style="36" min="2616" max="2814"/>
     <col width="1.6328125" customWidth="1" style="36" min="2815" max="2865"/>
     <col width="2.453125" customWidth="1" style="36" min="2866" max="2866"/>
     <col width="3.36328125" customWidth="1" style="36" min="2867" max="2867"/>
-    <col hidden="1" style="36" min="2868" max="2869"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="2868" max="2869"/>
     <col width="3.453125" customWidth="1" style="36" min="2870" max="2870"/>
     <col width="1.6328125" customWidth="1" style="36" min="2871" max="2871"/>
     <col width="9.08984375" customWidth="1" style="36" min="2872" max="3070"/>
     <col width="1.6328125" customWidth="1" style="36" min="3071" max="3121"/>
     <col width="2.453125" customWidth="1" style="36" min="3122" max="3122"/>
     <col width="3.36328125" customWidth="1" style="36" min="3123" max="3123"/>
-    <col hidden="1" style="36" min="3124" max="3125"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="3124" max="3125"/>
     <col width="3.453125" customWidth="1" style="36" min="3126" max="3126"/>
     <col width="1.6328125" customWidth="1" style="36" min="3127" max="3127"/>
     <col width="9.08984375" customWidth="1" style="36" min="3128" max="3326"/>
     <col width="1.6328125" customWidth="1" style="36" min="3327" max="3377"/>
     <col width="2.453125" customWidth="1" style="36" min="3378" max="3378"/>
     <col width="3.36328125" customWidth="1" style="36" min="3379" max="3379"/>
-    <col hidden="1" style="36" min="3380" max="3381"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="3380" max="3381"/>
     <col width="3.453125" customWidth="1" style="36" min="3382" max="3382"/>
     <col width="1.6328125" customWidth="1" style="36" min="3383" max="3383"/>
     <col width="9.08984375" customWidth="1" style="36" min="3384" max="3582"/>
     <col width="1.6328125" customWidth="1" style="36" min="3583" max="3633"/>
     <col width="2.453125" customWidth="1" style="36" min="3634" max="3634"/>
     <col width="3.36328125" customWidth="1" style="36" min="3635" max="3635"/>
-    <col hidden="1" style="36" min="3636" max="3637"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="3636" max="3637"/>
     <col width="3.453125" customWidth="1" style="36" min="3638" max="3638"/>
     <col width="1.6328125" customWidth="1" style="36" min="3639" max="3639"/>
     <col width="9.08984375" customWidth="1" style="36" min="3640" max="3838"/>
     <col width="1.6328125" customWidth="1" style="36" min="3839" max="3889"/>
     <col width="2.453125" customWidth="1" style="36" min="3890" max="3890"/>
     <col width="3.36328125" customWidth="1" style="36" min="3891" max="3891"/>
-    <col hidden="1" style="36" min="3892" max="3893"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="3892" max="3893"/>
     <col width="3.453125" customWidth="1" style="36" min="3894" max="3894"/>
     <col width="1.6328125" customWidth="1" style="36" min="3895" max="3895"/>
     <col width="9.08984375" customWidth="1" style="36" min="3896" max="4094"/>
     <col width="1.6328125" customWidth="1" style="36" min="4095" max="4145"/>
     <col width="2.453125" customWidth="1" style="36" min="4146" max="4146"/>
     <col width="3.36328125" customWidth="1" style="36" min="4147" max="4147"/>
-    <col hidden="1" style="36" min="4148" max="4149"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="4148" max="4149"/>
     <col width="3.453125" customWidth="1" style="36" min="4150" max="4150"/>
     <col width="1.6328125" customWidth="1" style="36" min="4151" max="4151"/>
     <col width="9.08984375" customWidth="1" style="36" min="4152" max="4350"/>
     <col width="1.6328125" customWidth="1" style="36" min="4351" max="4401"/>
     <col width="2.453125" customWidth="1" style="36" min="4402" max="4402"/>
     <col width="3.36328125" customWidth="1" style="36" min="4403" max="4403"/>
-    <col hidden="1" style="36" min="4404" max="4405"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="4404" max="4405"/>
     <col width="3.453125" customWidth="1" style="36" min="4406" max="4406"/>
     <col width="1.6328125" customWidth="1" style="36" min="4407" max="4407"/>
     <col width="9.08984375" customWidth="1" style="36" min="4408" max="4606"/>
     <col width="1.6328125" customWidth="1" style="36" min="4607" max="4657"/>
     <col width="2.453125" customWidth="1" style="36" min="4658" max="4658"/>
     <col width="3.36328125" customWidth="1" style="36" min="4659" max="4659"/>
-    <col hidden="1" style="36" min="4660" max="4661"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="4660" max="4661"/>
     <col width="3.453125" customWidth="1" style="36" min="4662" max="4662"/>
     <col width="1.6328125" customWidth="1" style="36" min="4663" max="4663"/>
     <col width="9.08984375" customWidth="1" style="36" min="4664" max="4862"/>
     <col width="1.6328125" customWidth="1" style="36" min="4863" max="4913"/>
     <col width="2.453125" customWidth="1" style="36" min="4914" max="4914"/>
     <col width="3.36328125" customWidth="1" style="36" min="4915" max="4915"/>
-    <col hidden="1" style="36" min="4916" max="4917"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="4916" max="4917"/>
     <col width="3.453125" customWidth="1" style="36" min="4918" max="4918"/>
     <col width="1.6328125" customWidth="1" style="36" min="4919" max="4919"/>
     <col width="9.08984375" customWidth="1" style="36" min="4920" max="5118"/>
     <col width="1.6328125" customWidth="1" style="36" min="5119" max="5169"/>
     <col width="2.453125" customWidth="1" style="36" min="5170" max="5170"/>
     <col width="3.36328125" customWidth="1" style="36" min="5171" max="5171"/>
-    <col hidden="1" style="36" min="5172" max="5173"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="5172" max="5173"/>
     <col width="3.453125" customWidth="1" style="36" min="5174" max="5174"/>
     <col width="1.6328125" customWidth="1" style="36" min="5175" max="5175"/>
     <col width="9.08984375" customWidth="1" style="36" min="5176" max="5374"/>
     <col width="1.6328125" customWidth="1" style="36" min="5375" max="5425"/>
     <col width="2.453125" customWidth="1" style="36" min="5426" max="5426"/>
     <col width="3.36328125" customWidth="1" style="36" min="5427" max="5427"/>
-    <col hidden="1" style="36" min="5428" max="5429"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="5428" max="5429"/>
     <col width="3.453125" customWidth="1" style="36" min="5430" max="5430"/>
     <col width="1.6328125" customWidth="1" style="36" min="5431" max="5431"/>
     <col width="9.08984375" customWidth="1" style="36" min="5432" max="5630"/>
     <col width="1.6328125" customWidth="1" style="36" min="5631" max="5681"/>
     <col width="2.453125" customWidth="1" style="36" min="5682" max="5682"/>
     <col width="3.36328125" customWidth="1" style="36" min="5683" max="5683"/>
-    <col hidden="1" style="36" min="5684" max="5685"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="5684" max="5685"/>
     <col width="3.453125" customWidth="1" style="36" min="5686" max="5686"/>
     <col width="1.6328125" customWidth="1" style="36" min="5687" max="5687"/>
     <col width="9.08984375" customWidth="1" style="36" min="5688" max="5886"/>
     <col width="1.6328125" customWidth="1" style="36" min="5887" max="5937"/>
     <col width="2.453125" customWidth="1" style="36" min="5938" max="5938"/>
     <col width="3.36328125" customWidth="1" style="36" min="5939" max="5939"/>
-    <col hidden="1" style="36" min="5940" max="5941"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="5940" max="5941"/>
     <col width="3.453125" customWidth="1" style="36" min="5942" max="5942"/>
     <col width="1.6328125" customWidth="1" style="36" min="5943" max="5943"/>
     <col width="9.08984375" customWidth="1" style="36" min="5944" max="6142"/>
     <col width="1.6328125" customWidth="1" style="36" min="6143" max="6193"/>
     <col width="2.453125" customWidth="1" style="36" min="6194" max="6194"/>
     <col width="3.36328125" customWidth="1" style="36" min="6195" max="6195"/>
-    <col hidden="1" style="36" min="6196" max="6197"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="6196" max="6197"/>
     <col width="3.453125" customWidth="1" style="36" min="6198" max="6198"/>
     <col width="1.6328125" customWidth="1" style="36" min="6199" max="6199"/>
     <col width="9.08984375" customWidth="1" style="36" min="6200" max="6398"/>
     <col width="1.6328125" customWidth="1" style="36" min="6399" max="6449"/>
     <col width="2.453125" customWidth="1" style="36" min="6450" max="6450"/>
     <col width="3.36328125" customWidth="1" style="36" min="6451" max="6451"/>
-    <col hidden="1" style="36" min="6452" max="6453"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="6452" max="6453"/>
     <col width="3.453125" customWidth="1" style="36" min="6454" max="6454"/>
     <col width="1.6328125" customWidth="1" style="36" min="6455" max="6455"/>
     <col width="9.08984375" customWidth="1" style="36" min="6456" max="6654"/>
     <col width="1.6328125" customWidth="1" style="36" min="6655" max="6705"/>
     <col width="2.453125" customWidth="1" style="36" min="6706" max="6706"/>
     <col width="3.36328125" customWidth="1" style="36" min="6707" max="6707"/>
-    <col hidden="1" style="36" min="6708" max="6709"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="6708" max="6709"/>
     <col width="3.453125" customWidth="1" style="36" min="6710" max="6710"/>
     <col width="1.6328125" customWidth="1" style="36" min="6711" max="6711"/>
     <col width="9.08984375" customWidth="1" style="36" min="6712" max="6910"/>
     <col width="1.6328125" customWidth="1" style="36" min="6911" max="6961"/>
     <col width="2.453125" customWidth="1" style="36" min="6962" max="6962"/>
     <col width="3.36328125" customWidth="1" style="36" min="6963" max="6963"/>
-    <col hidden="1" style="36" min="6964" max="6965"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="6964" max="6965"/>
     <col width="3.453125" customWidth="1" style="36" min="6966" max="6966"/>
     <col width="1.6328125" customWidth="1" style="36" min="6967" max="6967"/>
     <col width="9.08984375" customWidth="1" style="36" min="6968" max="7166"/>
     <col width="1.6328125" customWidth="1" style="36" min="7167" max="7217"/>
     <col width="2.453125" customWidth="1" style="36" min="7218" max="7218"/>
     <col width="3.36328125" customWidth="1" style="36" min="7219" max="7219"/>
-    <col hidden="1" style="36" min="7220" max="7221"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="7220" max="7221"/>
     <col width="3.453125" customWidth="1" style="36" min="7222" max="7222"/>
     <col width="1.6328125" customWidth="1" style="36" min="7223" max="7223"/>
     <col width="9.08984375" customWidth="1" style="36" min="7224" max="7422"/>
     <col width="1.6328125" customWidth="1" style="36" min="7423" max="7473"/>
     <col width="2.453125" customWidth="1" style="36" min="7474" max="7474"/>
     <col width="3.36328125" customWidth="1" style="36" min="7475" max="7475"/>
-    <col hidden="1" style="36" min="7476" max="7477"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="7476" max="7477"/>
     <col width="3.453125" customWidth="1" style="36" min="7478" max="7478"/>
     <col width="1.6328125" customWidth="1" style="36" min="7479" max="7479"/>
     <col width="9.08984375" customWidth="1" style="36" min="7480" max="7678"/>
     <col width="1.6328125" customWidth="1" style="36" min="7679" max="7729"/>
     <col width="2.453125" customWidth="1" style="36" min="7730" max="7730"/>
     <col width="3.36328125" customWidth="1" style="36" min="7731" max="7731"/>
-    <col hidden="1" style="36" min="7732" max="7733"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="7732" max="7733"/>
     <col width="3.453125" customWidth="1" style="36" min="7734" max="7734"/>
     <col width="1.6328125" customWidth="1" style="36" min="7735" max="7735"/>
     <col width="9.08984375" customWidth="1" style="36" min="7736" max="7934"/>
     <col width="1.6328125" customWidth="1" style="36" min="7935" max="7985"/>
     <col width="2.453125" customWidth="1" style="36" min="7986" max="7986"/>
     <col width="3.36328125" customWidth="1" style="36" min="7987" max="7987"/>
-    <col hidden="1" style="36" min="7988" max="7989"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="7988" max="7989"/>
     <col width="3.453125" customWidth="1" style="36" min="7990" max="7990"/>
     <col width="1.6328125" customWidth="1" style="36" min="7991" max="7991"/>
     <col width="9.08984375" customWidth="1" style="36" min="7992" max="8190"/>
     <col width="1.6328125" customWidth="1" style="36" min="8191" max="8241"/>
     <col width="2.453125" customWidth="1" style="36" min="8242" max="8242"/>
     <col width="3.36328125" customWidth="1" style="36" min="8243" max="8243"/>
-    <col hidden="1" style="36" min="8244" max="8245"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="8244" max="8245"/>
     <col width="3.453125" customWidth="1" style="36" min="8246" max="8246"/>
     <col width="1.6328125" customWidth="1" style="36" min="8247" max="8247"/>
     <col width="9.08984375" customWidth="1" style="36" min="8248" max="8446"/>
     <col width="1.6328125" customWidth="1" style="36" min="8447" max="8497"/>
     <col width="2.453125" customWidth="1" style="36" min="8498" max="8498"/>
     <col width="3.36328125" customWidth="1" style="36" min="8499" max="8499"/>
-    <col hidden="1" style="36" min="8500" max="8501"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="8500" max="8501"/>
     <col width="3.453125" customWidth="1" style="36" min="8502" max="8502"/>
     <col width="1.6328125" customWidth="1" style="36" min="8503" max="8503"/>
     <col width="9.08984375" customWidth="1" style="36" min="8504" max="8702"/>
     <col width="1.6328125" customWidth="1" style="36" min="8703" max="8753"/>
     <col width="2.453125" customWidth="1" style="36" min="8754" max="8754"/>
     <col width="3.36328125" customWidth="1" style="36" min="8755" max="8755"/>
-    <col hidden="1" style="36" min="8756" max="8757"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="8756" max="8757"/>
     <col width="3.453125" customWidth="1" style="36" min="8758" max="8758"/>
     <col width="1.6328125" customWidth="1" style="36" min="8759" max="8759"/>
     <col width="9.08984375" customWidth="1" style="36" min="8760" max="8958"/>
     <col width="1.6328125" customWidth="1" style="36" min="8959" max="9009"/>
     <col width="2.453125" customWidth="1" style="36" min="9010" max="9010"/>
     <col width="3.36328125" customWidth="1" style="36" min="9011" max="9011"/>
-    <col hidden="1" style="36" min="9012" max="9013"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="9012" max="9013"/>
     <col width="3.453125" customWidth="1" style="36" min="9014" max="9014"/>
     <col width="1.6328125" customWidth="1" style="36" min="9015" max="9015"/>
     <col width="9.08984375" customWidth="1" style="36" min="9016" max="9214"/>
     <col width="1.6328125" customWidth="1" style="36" min="9215" max="9265"/>
     <col width="2.453125" customWidth="1" style="36" min="9266" max="9266"/>
     <col width="3.36328125" customWidth="1" style="36" min="9267" max="9267"/>
-    <col hidden="1" style="36" min="9268" max="9269"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="9268" max="9269"/>
     <col width="3.453125" customWidth="1" style="36" min="9270" max="9270"/>
     <col width="1.6328125" customWidth="1" style="36" min="9271" max="9271"/>
     <col width="9.08984375" customWidth="1" style="36" min="9272" max="9470"/>
     <col width="1.6328125" customWidth="1" style="36" min="9471" max="9521"/>
     <col width="2.453125" customWidth="1" style="36" min="9522" max="9522"/>
     <col width="3.36328125" customWidth="1" style="36" min="9523" max="9523"/>
-    <col hidden="1" style="36" min="9524" max="9525"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="9524" max="9525"/>
     <col width="3.453125" customWidth="1" style="36" min="9526" max="9526"/>
     <col width="1.6328125" customWidth="1" style="36" min="9527" max="9527"/>
     <col width="9.08984375" customWidth="1" style="36" min="9528" max="9726"/>
     <col width="1.6328125" customWidth="1" style="36" min="9727" max="9777"/>
     <col width="2.453125" customWidth="1" style="36" min="9778" max="9778"/>
     <col width="3.36328125" customWidth="1" style="36" min="9779" max="9779"/>
-    <col hidden="1" style="36" min="9780" max="9781"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="9780" max="9781"/>
     <col width="3.453125" customWidth="1" style="36" min="9782" max="9782"/>
     <col width="1.6328125" customWidth="1" style="36" min="9783" max="9783"/>
     <col width="9.08984375" customWidth="1" style="36" min="9784" max="9982"/>
     <col width="1.6328125" customWidth="1" style="36" min="9983" max="10033"/>
     <col width="2.453125" customWidth="1" style="36" min="10034" max="10034"/>
     <col width="3.36328125" customWidth="1" style="36" min="10035" max="10035"/>
-    <col hidden="1" style="36" min="10036" max="10037"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="10036" max="10037"/>
     <col width="3.453125" customWidth="1" style="36" min="10038" max="10038"/>
     <col width="1.6328125" customWidth="1" style="36" min="10039" max="10039"/>
     <col width="9.08984375" customWidth="1" style="36" min="10040" max="10238"/>
     <col width="1.6328125" customWidth="1" style="36" min="10239" max="10289"/>
     <col width="2.453125" customWidth="1" style="36" min="10290" max="10290"/>
     <col width="3.36328125" customWidth="1" style="36" min="10291" max="10291"/>
-    <col hidden="1" style="36" min="10292" max="10293"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="10292" max="10293"/>
     <col width="3.453125" customWidth="1" style="36" min="10294" max="10294"/>
     <col width="1.6328125" customWidth="1" style="36" min="10295" max="10295"/>
     <col width="9.08984375" customWidth="1" style="36" min="10296" max="10494"/>
     <col width="1.6328125" customWidth="1" style="36" min="10495" max="10545"/>
     <col width="2.453125" customWidth="1" style="36" min="10546" max="10546"/>
     <col width="3.36328125" customWidth="1" style="36" min="10547" max="10547"/>
-    <col hidden="1" style="36" min="10548" max="10549"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="10548" max="10549"/>
     <col width="3.453125" customWidth="1" style="36" min="10550" max="10550"/>
     <col width="1.6328125" customWidth="1" style="36" min="10551" max="10551"/>
     <col width="9.08984375" customWidth="1" style="36" min="10552" max="10750"/>
     <col width="1.6328125" customWidth="1" style="36" min="10751" max="10801"/>
     <col width="2.453125" customWidth="1" style="36" min="10802" max="10802"/>
     <col width="3.36328125" customWidth="1" style="36" min="10803" max="10803"/>
-    <col hidden="1" style="36" min="10804" max="10805"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="10804" max="10805"/>
     <col width="3.453125" customWidth="1" style="36" min="10806" max="10806"/>
     <col width="1.6328125" customWidth="1" style="36" min="10807" max="10807"/>
     <col width="9.08984375" customWidth="1" style="36" min="10808" max="11006"/>
     <col width="1.6328125" customWidth="1" style="36" min="11007" max="11057"/>
     <col width="2.453125" customWidth="1" style="36" min="11058" max="11058"/>
     <col width="3.36328125" customWidth="1" style="36" min="11059" max="11059"/>
-    <col hidden="1" style="36" min="11060" max="11061"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="11060" max="11061"/>
     <col width="3.453125" customWidth="1" style="36" min="11062" max="11062"/>
     <col width="1.6328125" customWidth="1" style="36" min="11063" max="11063"/>
     <col width="9.08984375" customWidth="1" style="36" min="11064" max="11262"/>
     <col width="1.6328125" customWidth="1" style="36" min="11263" max="11313"/>
     <col width="2.453125" customWidth="1" style="36" min="11314" max="11314"/>
     <col width="3.36328125" customWidth="1" style="36" min="11315" max="11315"/>
-    <col hidden="1" style="36" min="11316" max="11317"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="11316" max="11317"/>
     <col width="3.453125" customWidth="1" style="36" min="11318" max="11318"/>
     <col width="1.6328125" customWidth="1" style="36" min="11319" max="11319"/>
     <col width="9.08984375" customWidth="1" style="36" min="11320" max="11518"/>
     <col width="1.6328125" customWidth="1" style="36" min="11519" max="11569"/>
     <col width="2.453125" customWidth="1" style="36" min="11570" max="11570"/>
     <col width="3.36328125" customWidth="1" style="36" min="11571" max="11571"/>
-    <col hidden="1" style="36" min="11572" max="11573"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="11572" max="11573"/>
     <col width="3.453125" customWidth="1" style="36" min="11574" max="11574"/>
     <col width="1.6328125" customWidth="1" style="36" min="11575" max="11575"/>
     <col width="9.08984375" customWidth="1" style="36" min="11576" max="11774"/>
     <col width="1.6328125" customWidth="1" style="36" min="11775" max="11825"/>
     <col width="2.453125" customWidth="1" style="36" min="11826" max="11826"/>
     <col width="3.36328125" customWidth="1" style="36" min="11827" max="11827"/>
-    <col hidden="1" style="36" min="11828" max="11829"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="11828" max="11829"/>
     <col width="3.453125" customWidth="1" style="36" min="11830" max="11830"/>
     <col width="1.6328125" customWidth="1" style="36" min="11831" max="11831"/>
     <col width="9.08984375" customWidth="1" style="36" min="11832" max="12030"/>
     <col width="1.6328125" customWidth="1" style="36" min="12031" max="12081"/>
     <col width="2.453125" customWidth="1" style="36" min="12082" max="12082"/>
     <col width="3.36328125" customWidth="1" style="36" min="12083" max="12083"/>
-    <col hidden="1" style="36" min="12084" max="12085"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="12084" max="12085"/>
     <col width="3.453125" customWidth="1" style="36" min="12086" max="12086"/>
     <col width="1.6328125" customWidth="1" style="36" min="12087" max="12087"/>
     <col width="9.08984375" customWidth="1" style="36" min="12088" max="12286"/>
     <col width="1.6328125" customWidth="1" style="36" min="12287" max="12337"/>
     <col width="2.453125" customWidth="1" style="36" min="12338" max="12338"/>
     <col width="3.36328125" customWidth="1" style="36" min="12339" max="12339"/>
-    <col hidden="1" style="36" min="12340" max="12341"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="12340" max="12341"/>
     <col width="3.453125" customWidth="1" style="36" min="12342" max="12342"/>
     <col width="1.6328125" customWidth="1" style="36" min="12343" max="12343"/>
     <col width="9.08984375" customWidth="1" style="36" min="12344" max="12542"/>
     <col width="1.6328125" customWidth="1" style="36" min="12543" max="12593"/>
     <col width="2.453125" customWidth="1" style="36" min="12594" max="12594"/>
     <col width="3.36328125" customWidth="1" style="36" min="12595" max="12595"/>
-    <col hidden="1" style="36" min="12596" max="12597"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="12596" max="12597"/>
     <col width="3.453125" customWidth="1" style="36" min="12598" max="12598"/>
     <col width="1.6328125" customWidth="1" style="36" min="12599" max="12599"/>
     <col width="9.08984375" customWidth="1" style="36" min="12600" max="12798"/>
     <col width="1.6328125" customWidth="1" style="36" min="12799" max="12849"/>
     <col width="2.453125" customWidth="1" style="36" min="12850" max="12850"/>
     <col width="3.36328125" customWidth="1" style="36" min="12851" max="12851"/>
-    <col hidden="1" style="36" min="12852" max="12853"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="12852" max="12853"/>
     <col width="3.453125" customWidth="1" style="36" min="12854" max="12854"/>
     <col width="1.6328125" customWidth="1" style="36" min="12855" max="12855"/>
     <col width="9.08984375" customWidth="1" style="36" min="12856" max="13054"/>
     <col width="1.6328125" customWidth="1" style="36" min="13055" max="13105"/>
     <col width="2.453125" customWidth="1" style="36" min="13106" max="13106"/>
     <col width="3.36328125" customWidth="1" style="36" min="13107" max="13107"/>
-    <col hidden="1" style="36" min="13108" max="13109"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="13108" max="13109"/>
     <col width="3.453125" customWidth="1" style="36" min="13110" max="13110"/>
     <col width="1.6328125" customWidth="1" style="36" min="13111" max="13111"/>
     <col width="9.08984375" customWidth="1" style="36" min="13112" max="13310"/>
     <col width="1.6328125" customWidth="1" style="36" min="13311" max="13361"/>
     <col width="2.453125" customWidth="1" style="36" min="13362" max="13362"/>
     <col width="3.36328125" customWidth="1" style="36" min="13363" max="13363"/>
-    <col hidden="1" style="36" min="13364" max="13365"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="13364" max="13365"/>
     <col width="3.453125" customWidth="1" style="36" min="13366" max="13366"/>
     <col width="1.6328125" customWidth="1" style="36" min="13367" max="13367"/>
     <col width="9.08984375" customWidth="1" style="36" min="13368" max="13566"/>
     <col width="1.6328125" customWidth="1" style="36" min="13567" max="13617"/>
     <col width="2.453125" customWidth="1" style="36" min="13618" max="13618"/>
     <col width="3.36328125" customWidth="1" style="36" min="13619" max="13619"/>
-    <col hidden="1" style="36" min="13620" max="13621"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="13620" max="13621"/>
     <col width="3.453125" customWidth="1" style="36" min="13622" max="13622"/>
     <col width="1.6328125" customWidth="1" style="36" min="13623" max="13623"/>
     <col width="9.08984375" customWidth="1" style="36" min="13624" max="13822"/>
     <col width="1.6328125" customWidth="1" style="36" min="13823" max="13873"/>
     <col width="2.453125" customWidth="1" style="36" min="13874" max="13874"/>
     <col width="3.36328125" customWidth="1" style="36" min="13875" max="13875"/>
-    <col hidden="1" style="36" min="13876" max="13877"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="13876" max="13877"/>
     <col width="3.453125" customWidth="1" style="36" min="13878" max="13878"/>
     <col width="1.6328125" customWidth="1" style="36" min="13879" max="13879"/>
     <col width="9.08984375" customWidth="1" style="36" min="13880" max="14078"/>
     <col width="1.6328125" customWidth="1" style="36" min="14079" max="14129"/>
     <col width="2.453125" customWidth="1" style="36" min="14130" max="14130"/>
     <col width="3.36328125" customWidth="1" style="36" min="14131" max="14131"/>
-    <col hidden="1" style="36" min="14132" max="14133"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="14132" max="14133"/>
     <col width="3.453125" customWidth="1" style="36" min="14134" max="14134"/>
     <col width="1.6328125" customWidth="1" style="36" min="14135" max="14135"/>
     <col width="9.08984375" customWidth="1" style="36" min="14136" max="14334"/>
     <col width="1.6328125" customWidth="1" style="36" min="14335" max="14385"/>
     <col width="2.453125" customWidth="1" style="36" min="14386" max="14386"/>
     <col width="3.36328125" customWidth="1" style="36" min="14387" max="14387"/>
-    <col hidden="1" style="36" min="14388" max="14389"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="14388" max="14389"/>
     <col width="3.453125" customWidth="1" style="36" min="14390" max="14390"/>
     <col width="1.6328125" customWidth="1" style="36" min="14391" max="14391"/>
     <col width="9.08984375" customWidth="1" style="36" min="14392" max="14590"/>
     <col width="1.6328125" customWidth="1" style="36" min="14591" max="14641"/>
     <col width="2.453125" customWidth="1" style="36" min="14642" max="14642"/>
     <col width="3.36328125" customWidth="1" style="36" min="14643" max="14643"/>
-    <col hidden="1" style="36" min="14644" max="14645"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="14644" max="14645"/>
     <col width="3.453125" customWidth="1" style="36" min="14646" max="14646"/>
     <col width="1.6328125" customWidth="1" style="36" min="14647" max="14647"/>
     <col width="9.08984375" customWidth="1" style="36" min="14648" max="14846"/>
     <col width="1.6328125" customWidth="1" style="36" min="14847" max="14897"/>
     <col width="2.453125" customWidth="1" style="36" min="14898" max="14898"/>
     <col width="3.36328125" customWidth="1" style="36" min="14899" max="14899"/>
-    <col hidden="1" style="36" min="14900" max="14901"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="14900" max="14901"/>
     <col width="3.453125" customWidth="1" style="36" min="14902" max="14902"/>
     <col width="1.6328125" customWidth="1" style="36" min="14903" max="14903"/>
     <col width="9.08984375" customWidth="1" style="36" min="14904" max="15102"/>
     <col width="1.6328125" customWidth="1" style="36" min="15103" max="15153"/>
     <col width="2.453125" customWidth="1" style="36" min="15154" max="15154"/>
     <col width="3.36328125" customWidth="1" style="36" min="15155" max="15155"/>
-    <col hidden="1" style="36" min="15156" max="15157"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="15156" max="15157"/>
     <col width="3.453125" customWidth="1" style="36" min="15158" max="15158"/>
     <col width="1.6328125" customWidth="1" style="36" min="15159" max="15159"/>
     <col width="9.08984375" customWidth="1" style="36" min="15160" max="15358"/>
     <col width="1.6328125" customWidth="1" style="36" min="15359" max="15409"/>
     <col width="2.453125" customWidth="1" style="36" min="15410" max="15410"/>
     <col width="3.36328125" customWidth="1" style="36" min="15411" max="15411"/>
-    <col hidden="1" style="36" min="15412" max="15413"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="15412" max="15413"/>
     <col width="3.453125" customWidth="1" style="36" min="15414" max="15414"/>
     <col width="1.6328125" customWidth="1" style="36" min="15415" max="15415"/>
     <col width="9.08984375" customWidth="1" style="36" min="15416" max="15614"/>
     <col width="1.6328125" customWidth="1" style="36" min="15615" max="15665"/>
     <col width="2.453125" customWidth="1" style="36" min="15666" max="15666"/>
     <col width="3.36328125" customWidth="1" style="36" min="15667" max="15667"/>
-    <col hidden="1" style="36" min="15668" max="15669"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="15668" max="15669"/>
     <col width="3.453125" customWidth="1" style="36" min="15670" max="15670"/>
     <col width="1.6328125" customWidth="1" style="36" min="15671" max="15671"/>
     <col width="9.08984375" customWidth="1" style="36" min="15672" max="15870"/>
     <col width="1.6328125" customWidth="1" style="36" min="15871" max="15921"/>
     <col width="2.453125" customWidth="1" style="36" min="15922" max="15922"/>
     <col width="3.36328125" customWidth="1" style="36" min="15923" max="15923"/>
-    <col hidden="1" style="36" min="15924" max="15925"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="15924" max="15925"/>
     <col width="3.453125" customWidth="1" style="36" min="15926" max="15926"/>
     <col width="1.6328125" customWidth="1" style="36" min="15927" max="15927"/>
     <col width="9.08984375" customWidth="1" style="36" min="15928" max="16126"/>
     <col width="1.6328125" customWidth="1" style="36" min="16127" max="16177"/>
     <col width="2.453125" customWidth="1" style="36" min="16178" max="16178"/>
     <col width="3.36328125" customWidth="1" style="36" min="16179" max="16179"/>
-    <col hidden="1" style="36" min="16180" max="16181"/>
+    <col hidden="1" width="13" customWidth="1" style="36" min="16180" max="16181"/>
     <col width="3.453125" customWidth="1" style="36" min="16182" max="16182"/>
     <col width="1.6328125" customWidth="1" style="36" min="16183" max="16183"/>
     <col width="9.08984375" customWidth="1" style="36" min="16184" max="16384"/>
@@ -3226,7 +3226,7 @@
     <row r="34" ht="14.25" customHeight="1" s="191"/>
     <row r="35" ht="19.5" customHeight="1" s="191"/>
     <row r="36" ht="17.25" customHeight="1" s="191"/>
-    <row r="37" ht="3" customHeight="1" s="191">
+    <row r="37" ht="12" customHeight="1" s="191">
       <c r="A37" s="235" t="n"/>
       <c r="B37" s="235" t="n"/>
       <c r="C37" s="235" t="n"/>
@@ -4105,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH46"/>
+  <dimension ref="A1:BC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.5"/>
   <cols>
     <col width="1.6328125" customWidth="1" style="237" min="1" max="2"/>
@@ -4117,441 +4117,441 @@
     <col width="1.6328125" customWidth="1" style="237" min="204" max="254"/>
     <col width="2.453125" customWidth="1" style="237" min="255" max="255"/>
     <col width="3.36328125" customWidth="1" style="237" min="256" max="256"/>
-    <col hidden="1" style="237" min="257" max="258"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="257" max="258"/>
     <col width="3.453125" customWidth="1" style="237" min="259" max="259"/>
     <col width="1.6328125" customWidth="1" style="237" min="260" max="260"/>
     <col width="9.08984375" customWidth="1" style="237" min="261" max="459"/>
     <col width="1.6328125" customWidth="1" style="237" min="460" max="510"/>
     <col width="2.453125" customWidth="1" style="237" min="511" max="511"/>
     <col width="3.36328125" customWidth="1" style="237" min="512" max="512"/>
-    <col hidden="1" style="237" min="513" max="514"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="513" max="514"/>
     <col width="3.453125" customWidth="1" style="237" min="515" max="515"/>
     <col width="1.6328125" customWidth="1" style="237" min="516" max="516"/>
     <col width="9.08984375" customWidth="1" style="237" min="517" max="715"/>
     <col width="1.6328125" customWidth="1" style="237" min="716" max="766"/>
     <col width="2.453125" customWidth="1" style="237" min="767" max="767"/>
     <col width="3.36328125" customWidth="1" style="237" min="768" max="768"/>
-    <col hidden="1" style="237" min="769" max="770"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="769" max="770"/>
     <col width="3.453125" customWidth="1" style="237" min="771" max="771"/>
     <col width="1.6328125" customWidth="1" style="237" min="772" max="772"/>
     <col width="9.08984375" customWidth="1" style="237" min="773" max="971"/>
     <col width="1.6328125" customWidth="1" style="237" min="972" max="1022"/>
     <col width="2.453125" customWidth="1" style="237" min="1023" max="1023"/>
     <col width="3.36328125" customWidth="1" style="237" min="1024" max="1024"/>
-    <col hidden="1" style="237" min="1025" max="1026"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="1025" max="1026"/>
     <col width="3.453125" customWidth="1" style="237" min="1027" max="1027"/>
     <col width="1.6328125" customWidth="1" style="237" min="1028" max="1028"/>
     <col width="9.08984375" customWidth="1" style="237" min="1029" max="1227"/>
     <col width="1.6328125" customWidth="1" style="237" min="1228" max="1278"/>
     <col width="2.453125" customWidth="1" style="237" min="1279" max="1279"/>
     <col width="3.36328125" customWidth="1" style="237" min="1280" max="1280"/>
-    <col hidden="1" style="237" min="1281" max="1282"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="1281" max="1282"/>
     <col width="3.453125" customWidth="1" style="237" min="1283" max="1283"/>
     <col width="1.6328125" customWidth="1" style="237" min="1284" max="1284"/>
     <col width="9.08984375" customWidth="1" style="237" min="1285" max="1483"/>
     <col width="1.6328125" customWidth="1" style="237" min="1484" max="1534"/>
     <col width="2.453125" customWidth="1" style="237" min="1535" max="1535"/>
     <col width="3.36328125" customWidth="1" style="237" min="1536" max="1536"/>
-    <col hidden="1" style="237" min="1537" max="1538"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="1537" max="1538"/>
     <col width="3.453125" customWidth="1" style="237" min="1539" max="1539"/>
     <col width="1.6328125" customWidth="1" style="237" min="1540" max="1540"/>
     <col width="9.08984375" customWidth="1" style="237" min="1541" max="1739"/>
     <col width="1.6328125" customWidth="1" style="237" min="1740" max="1790"/>
     <col width="2.453125" customWidth="1" style="237" min="1791" max="1791"/>
     <col width="3.36328125" customWidth="1" style="237" min="1792" max="1792"/>
-    <col hidden="1" style="237" min="1793" max="1794"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="1793" max="1794"/>
     <col width="3.453125" customWidth="1" style="237" min="1795" max="1795"/>
     <col width="1.6328125" customWidth="1" style="237" min="1796" max="1796"/>
     <col width="9.08984375" customWidth="1" style="237" min="1797" max="1995"/>
     <col width="1.6328125" customWidth="1" style="237" min="1996" max="2046"/>
     <col width="2.453125" customWidth="1" style="237" min="2047" max="2047"/>
     <col width="3.36328125" customWidth="1" style="237" min="2048" max="2048"/>
-    <col hidden="1" style="237" min="2049" max="2050"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="2049" max="2050"/>
     <col width="3.453125" customWidth="1" style="237" min="2051" max="2051"/>
     <col width="1.6328125" customWidth="1" style="237" min="2052" max="2052"/>
     <col width="9.08984375" customWidth="1" style="237" min="2053" max="2251"/>
     <col width="1.6328125" customWidth="1" style="237" min="2252" max="2302"/>
     <col width="2.453125" customWidth="1" style="237" min="2303" max="2303"/>
     <col width="3.36328125" customWidth="1" style="237" min="2304" max="2304"/>
-    <col hidden="1" style="237" min="2305" max="2306"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="2305" max="2306"/>
     <col width="3.453125" customWidth="1" style="237" min="2307" max="2307"/>
     <col width="1.6328125" customWidth="1" style="237" min="2308" max="2308"/>
     <col width="9.08984375" customWidth="1" style="237" min="2309" max="2507"/>
     <col width="1.6328125" customWidth="1" style="237" min="2508" max="2558"/>
     <col width="2.453125" customWidth="1" style="237" min="2559" max="2559"/>
     <col width="3.36328125" customWidth="1" style="237" min="2560" max="2560"/>
-    <col hidden="1" style="237" min="2561" max="2562"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="2561" max="2562"/>
     <col width="3.453125" customWidth="1" style="237" min="2563" max="2563"/>
     <col width="1.6328125" customWidth="1" style="237" min="2564" max="2564"/>
     <col width="9.08984375" customWidth="1" style="237" min="2565" max="2763"/>
     <col width="1.6328125" customWidth="1" style="237" min="2764" max="2814"/>
     <col width="2.453125" customWidth="1" style="237" min="2815" max="2815"/>
     <col width="3.36328125" customWidth="1" style="237" min="2816" max="2816"/>
-    <col hidden="1" style="237" min="2817" max="2818"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="2817" max="2818"/>
     <col width="3.453125" customWidth="1" style="237" min="2819" max="2819"/>
     <col width="1.6328125" customWidth="1" style="237" min="2820" max="2820"/>
     <col width="9.08984375" customWidth="1" style="237" min="2821" max="3019"/>
     <col width="1.6328125" customWidth="1" style="237" min="3020" max="3070"/>
     <col width="2.453125" customWidth="1" style="237" min="3071" max="3071"/>
     <col width="3.36328125" customWidth="1" style="237" min="3072" max="3072"/>
-    <col hidden="1" style="237" min="3073" max="3074"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="3073" max="3074"/>
     <col width="3.453125" customWidth="1" style="237" min="3075" max="3075"/>
     <col width="1.6328125" customWidth="1" style="237" min="3076" max="3076"/>
     <col width="9.08984375" customWidth="1" style="237" min="3077" max="3275"/>
     <col width="1.6328125" customWidth="1" style="237" min="3276" max="3326"/>
     <col width="2.453125" customWidth="1" style="237" min="3327" max="3327"/>
     <col width="3.36328125" customWidth="1" style="237" min="3328" max="3328"/>
-    <col hidden="1" style="237" min="3329" max="3330"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="3329" max="3330"/>
     <col width="3.453125" customWidth="1" style="237" min="3331" max="3331"/>
     <col width="1.6328125" customWidth="1" style="237" min="3332" max="3332"/>
     <col width="9.08984375" customWidth="1" style="237" min="3333" max="3531"/>
     <col width="1.6328125" customWidth="1" style="237" min="3532" max="3582"/>
     <col width="2.453125" customWidth="1" style="237" min="3583" max="3583"/>
     <col width="3.36328125" customWidth="1" style="237" min="3584" max="3584"/>
-    <col hidden="1" style="237" min="3585" max="3586"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="3585" max="3586"/>
     <col width="3.453125" customWidth="1" style="237" min="3587" max="3587"/>
     <col width="1.6328125" customWidth="1" style="237" min="3588" max="3588"/>
     <col width="9.08984375" customWidth="1" style="237" min="3589" max="3787"/>
     <col width="1.6328125" customWidth="1" style="237" min="3788" max="3838"/>
     <col width="2.453125" customWidth="1" style="237" min="3839" max="3839"/>
     <col width="3.36328125" customWidth="1" style="237" min="3840" max="3840"/>
-    <col hidden="1" style="237" min="3841" max="3842"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="3841" max="3842"/>
     <col width="3.453125" customWidth="1" style="237" min="3843" max="3843"/>
     <col width="1.6328125" customWidth="1" style="237" min="3844" max="3844"/>
     <col width="9.08984375" customWidth="1" style="237" min="3845" max="4043"/>
     <col width="1.6328125" customWidth="1" style="237" min="4044" max="4094"/>
     <col width="2.453125" customWidth="1" style="237" min="4095" max="4095"/>
     <col width="3.36328125" customWidth="1" style="237" min="4096" max="4096"/>
-    <col hidden="1" style="237" min="4097" max="4098"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="4097" max="4098"/>
     <col width="3.453125" customWidth="1" style="237" min="4099" max="4099"/>
     <col width="1.6328125" customWidth="1" style="237" min="4100" max="4100"/>
     <col width="9.08984375" customWidth="1" style="237" min="4101" max="4299"/>
     <col width="1.6328125" customWidth="1" style="237" min="4300" max="4350"/>
     <col width="2.453125" customWidth="1" style="237" min="4351" max="4351"/>
     <col width="3.36328125" customWidth="1" style="237" min="4352" max="4352"/>
-    <col hidden="1" style="237" min="4353" max="4354"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="4353" max="4354"/>
     <col width="3.453125" customWidth="1" style="237" min="4355" max="4355"/>
     <col width="1.6328125" customWidth="1" style="237" min="4356" max="4356"/>
     <col width="9.08984375" customWidth="1" style="237" min="4357" max="4555"/>
     <col width="1.6328125" customWidth="1" style="237" min="4556" max="4606"/>
     <col width="2.453125" customWidth="1" style="237" min="4607" max="4607"/>
     <col width="3.36328125" customWidth="1" style="237" min="4608" max="4608"/>
-    <col hidden="1" style="237" min="4609" max="4610"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="4609" max="4610"/>
     <col width="3.453125" customWidth="1" style="237" min="4611" max="4611"/>
     <col width="1.6328125" customWidth="1" style="237" min="4612" max="4612"/>
     <col width="9.08984375" customWidth="1" style="237" min="4613" max="4811"/>
     <col width="1.6328125" customWidth="1" style="237" min="4812" max="4862"/>
     <col width="2.453125" customWidth="1" style="237" min="4863" max="4863"/>
     <col width="3.36328125" customWidth="1" style="237" min="4864" max="4864"/>
-    <col hidden="1" style="237" min="4865" max="4866"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="4865" max="4866"/>
     <col width="3.453125" customWidth="1" style="237" min="4867" max="4867"/>
     <col width="1.6328125" customWidth="1" style="237" min="4868" max="4868"/>
     <col width="9.08984375" customWidth="1" style="237" min="4869" max="5067"/>
     <col width="1.6328125" customWidth="1" style="237" min="5068" max="5118"/>
     <col width="2.453125" customWidth="1" style="237" min="5119" max="5119"/>
     <col width="3.36328125" customWidth="1" style="237" min="5120" max="5120"/>
-    <col hidden="1" style="237" min="5121" max="5122"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="5121" max="5122"/>
     <col width="3.453125" customWidth="1" style="237" min="5123" max="5123"/>
     <col width="1.6328125" customWidth="1" style="237" min="5124" max="5124"/>
     <col width="9.08984375" customWidth="1" style="237" min="5125" max="5323"/>
     <col width="1.6328125" customWidth="1" style="237" min="5324" max="5374"/>
     <col width="2.453125" customWidth="1" style="237" min="5375" max="5375"/>
     <col width="3.36328125" customWidth="1" style="237" min="5376" max="5376"/>
-    <col hidden="1" style="237" min="5377" max="5378"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="5377" max="5378"/>
     <col width="3.453125" customWidth="1" style="237" min="5379" max="5379"/>
     <col width="1.6328125" customWidth="1" style="237" min="5380" max="5380"/>
     <col width="9.08984375" customWidth="1" style="237" min="5381" max="5579"/>
     <col width="1.6328125" customWidth="1" style="237" min="5580" max="5630"/>
     <col width="2.453125" customWidth="1" style="237" min="5631" max="5631"/>
     <col width="3.36328125" customWidth="1" style="237" min="5632" max="5632"/>
-    <col hidden="1" style="237" min="5633" max="5634"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="5633" max="5634"/>
     <col width="3.453125" customWidth="1" style="237" min="5635" max="5635"/>
     <col width="1.6328125" customWidth="1" style="237" min="5636" max="5636"/>
     <col width="9.08984375" customWidth="1" style="237" min="5637" max="5835"/>
     <col width="1.6328125" customWidth="1" style="237" min="5836" max="5886"/>
     <col width="2.453125" customWidth="1" style="237" min="5887" max="5887"/>
     <col width="3.36328125" customWidth="1" style="237" min="5888" max="5888"/>
-    <col hidden="1" style="237" min="5889" max="5890"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="5889" max="5890"/>
     <col width="3.453125" customWidth="1" style="237" min="5891" max="5891"/>
     <col width="1.6328125" customWidth="1" style="237" min="5892" max="5892"/>
     <col width="9.08984375" customWidth="1" style="237" min="5893" max="6091"/>
     <col width="1.6328125" customWidth="1" style="237" min="6092" max="6142"/>
     <col width="2.453125" customWidth="1" style="237" min="6143" max="6143"/>
     <col width="3.36328125" customWidth="1" style="237" min="6144" max="6144"/>
-    <col hidden="1" style="237" min="6145" max="6146"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="6145" max="6146"/>
     <col width="3.453125" customWidth="1" style="237" min="6147" max="6147"/>
     <col width="1.6328125" customWidth="1" style="237" min="6148" max="6148"/>
     <col width="9.08984375" customWidth="1" style="237" min="6149" max="6347"/>
     <col width="1.6328125" customWidth="1" style="237" min="6348" max="6398"/>
     <col width="2.453125" customWidth="1" style="237" min="6399" max="6399"/>
     <col width="3.36328125" customWidth="1" style="237" min="6400" max="6400"/>
-    <col hidden="1" style="237" min="6401" max="6402"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="6401" max="6402"/>
     <col width="3.453125" customWidth="1" style="237" min="6403" max="6403"/>
     <col width="1.6328125" customWidth="1" style="237" min="6404" max="6404"/>
     <col width="9.08984375" customWidth="1" style="237" min="6405" max="6603"/>
     <col width="1.6328125" customWidth="1" style="237" min="6604" max="6654"/>
     <col width="2.453125" customWidth="1" style="237" min="6655" max="6655"/>
     <col width="3.36328125" customWidth="1" style="237" min="6656" max="6656"/>
-    <col hidden="1" style="237" min="6657" max="6658"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="6657" max="6658"/>
     <col width="3.453125" customWidth="1" style="237" min="6659" max="6659"/>
     <col width="1.6328125" customWidth="1" style="237" min="6660" max="6660"/>
     <col width="9.08984375" customWidth="1" style="237" min="6661" max="6859"/>
     <col width="1.6328125" customWidth="1" style="237" min="6860" max="6910"/>
     <col width="2.453125" customWidth="1" style="237" min="6911" max="6911"/>
     <col width="3.36328125" customWidth="1" style="237" min="6912" max="6912"/>
-    <col hidden="1" style="237" min="6913" max="6914"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="6913" max="6914"/>
     <col width="3.453125" customWidth="1" style="237" min="6915" max="6915"/>
     <col width="1.6328125" customWidth="1" style="237" min="6916" max="6916"/>
     <col width="9.08984375" customWidth="1" style="237" min="6917" max="7115"/>
     <col width="1.6328125" customWidth="1" style="237" min="7116" max="7166"/>
     <col width="2.453125" customWidth="1" style="237" min="7167" max="7167"/>
     <col width="3.36328125" customWidth="1" style="237" min="7168" max="7168"/>
-    <col hidden="1" style="237" min="7169" max="7170"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="7169" max="7170"/>
     <col width="3.453125" customWidth="1" style="237" min="7171" max="7171"/>
     <col width="1.6328125" customWidth="1" style="237" min="7172" max="7172"/>
     <col width="9.08984375" customWidth="1" style="237" min="7173" max="7371"/>
     <col width="1.6328125" customWidth="1" style="237" min="7372" max="7422"/>
     <col width="2.453125" customWidth="1" style="237" min="7423" max="7423"/>
     <col width="3.36328125" customWidth="1" style="237" min="7424" max="7424"/>
-    <col hidden="1" style="237" min="7425" max="7426"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="7425" max="7426"/>
     <col width="3.453125" customWidth="1" style="237" min="7427" max="7427"/>
     <col width="1.6328125" customWidth="1" style="237" min="7428" max="7428"/>
     <col width="9.08984375" customWidth="1" style="237" min="7429" max="7627"/>
     <col width="1.6328125" customWidth="1" style="237" min="7628" max="7678"/>
     <col width="2.453125" customWidth="1" style="237" min="7679" max="7679"/>
     <col width="3.36328125" customWidth="1" style="237" min="7680" max="7680"/>
-    <col hidden="1" style="237" min="7681" max="7682"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="7681" max="7682"/>
     <col width="3.453125" customWidth="1" style="237" min="7683" max="7683"/>
     <col width="1.6328125" customWidth="1" style="237" min="7684" max="7684"/>
     <col width="9.08984375" customWidth="1" style="237" min="7685" max="7883"/>
     <col width="1.6328125" customWidth="1" style="237" min="7884" max="7934"/>
     <col width="2.453125" customWidth="1" style="237" min="7935" max="7935"/>
     <col width="3.36328125" customWidth="1" style="237" min="7936" max="7936"/>
-    <col hidden="1" style="237" min="7937" max="7938"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="7937" max="7938"/>
     <col width="3.453125" customWidth="1" style="237" min="7939" max="7939"/>
     <col width="1.6328125" customWidth="1" style="237" min="7940" max="7940"/>
     <col width="9.08984375" customWidth="1" style="237" min="7941" max="8139"/>
     <col width="1.6328125" customWidth="1" style="237" min="8140" max="8190"/>
     <col width="2.453125" customWidth="1" style="237" min="8191" max="8191"/>
     <col width="3.36328125" customWidth="1" style="237" min="8192" max="8192"/>
-    <col hidden="1" style="237" min="8193" max="8194"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="8193" max="8194"/>
     <col width="3.453125" customWidth="1" style="237" min="8195" max="8195"/>
     <col width="1.6328125" customWidth="1" style="237" min="8196" max="8196"/>
     <col width="9.08984375" customWidth="1" style="237" min="8197" max="8395"/>
     <col width="1.6328125" customWidth="1" style="237" min="8396" max="8446"/>
     <col width="2.453125" customWidth="1" style="237" min="8447" max="8447"/>
     <col width="3.36328125" customWidth="1" style="237" min="8448" max="8448"/>
-    <col hidden="1" style="237" min="8449" max="8450"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="8449" max="8450"/>
     <col width="3.453125" customWidth="1" style="237" min="8451" max="8451"/>
     <col width="1.6328125" customWidth="1" style="237" min="8452" max="8452"/>
     <col width="9.08984375" customWidth="1" style="237" min="8453" max="8651"/>
     <col width="1.6328125" customWidth="1" style="237" min="8652" max="8702"/>
     <col width="2.453125" customWidth="1" style="237" min="8703" max="8703"/>
     <col width="3.36328125" customWidth="1" style="237" min="8704" max="8704"/>
-    <col hidden="1" style="237" min="8705" max="8706"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="8705" max="8706"/>
     <col width="3.453125" customWidth="1" style="237" min="8707" max="8707"/>
     <col width="1.6328125" customWidth="1" style="237" min="8708" max="8708"/>
     <col width="9.08984375" customWidth="1" style="237" min="8709" max="8907"/>
     <col width="1.6328125" customWidth="1" style="237" min="8908" max="8958"/>
     <col width="2.453125" customWidth="1" style="237" min="8959" max="8959"/>
     <col width="3.36328125" customWidth="1" style="237" min="8960" max="8960"/>
-    <col hidden="1" style="237" min="8961" max="8962"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="8961" max="8962"/>
     <col width="3.453125" customWidth="1" style="237" min="8963" max="8963"/>
     <col width="1.6328125" customWidth="1" style="237" min="8964" max="8964"/>
     <col width="9.08984375" customWidth="1" style="237" min="8965" max="9163"/>
     <col width="1.6328125" customWidth="1" style="237" min="9164" max="9214"/>
     <col width="2.453125" customWidth="1" style="237" min="9215" max="9215"/>
     <col width="3.36328125" customWidth="1" style="237" min="9216" max="9216"/>
-    <col hidden="1" style="237" min="9217" max="9218"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="9217" max="9218"/>
     <col width="3.453125" customWidth="1" style="237" min="9219" max="9219"/>
     <col width="1.6328125" customWidth="1" style="237" min="9220" max="9220"/>
     <col width="9.08984375" customWidth="1" style="237" min="9221" max="9419"/>
     <col width="1.6328125" customWidth="1" style="237" min="9420" max="9470"/>
     <col width="2.453125" customWidth="1" style="237" min="9471" max="9471"/>
     <col width="3.36328125" customWidth="1" style="237" min="9472" max="9472"/>
-    <col hidden="1" style="237" min="9473" max="9474"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="9473" max="9474"/>
     <col width="3.453125" customWidth="1" style="237" min="9475" max="9475"/>
     <col width="1.6328125" customWidth="1" style="237" min="9476" max="9476"/>
     <col width="9.08984375" customWidth="1" style="237" min="9477" max="9675"/>
     <col width="1.6328125" customWidth="1" style="237" min="9676" max="9726"/>
     <col width="2.453125" customWidth="1" style="237" min="9727" max="9727"/>
     <col width="3.36328125" customWidth="1" style="237" min="9728" max="9728"/>
-    <col hidden="1" style="237" min="9729" max="9730"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="9729" max="9730"/>
     <col width="3.453125" customWidth="1" style="237" min="9731" max="9731"/>
     <col width="1.6328125" customWidth="1" style="237" min="9732" max="9732"/>
     <col width="9.08984375" customWidth="1" style="237" min="9733" max="9931"/>
     <col width="1.6328125" customWidth="1" style="237" min="9932" max="9982"/>
     <col width="2.453125" customWidth="1" style="237" min="9983" max="9983"/>
     <col width="3.36328125" customWidth="1" style="237" min="9984" max="9984"/>
-    <col hidden="1" style="237" min="9985" max="9986"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="9985" max="9986"/>
     <col width="3.453125" customWidth="1" style="237" min="9987" max="9987"/>
     <col width="1.6328125" customWidth="1" style="237" min="9988" max="9988"/>
     <col width="9.08984375" customWidth="1" style="237" min="9989" max="10187"/>
     <col width="1.6328125" customWidth="1" style="237" min="10188" max="10238"/>
     <col width="2.453125" customWidth="1" style="237" min="10239" max="10239"/>
     <col width="3.36328125" customWidth="1" style="237" min="10240" max="10240"/>
-    <col hidden="1" style="237" min="10241" max="10242"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="10241" max="10242"/>
     <col width="3.453125" customWidth="1" style="237" min="10243" max="10243"/>
     <col width="1.6328125" customWidth="1" style="237" min="10244" max="10244"/>
     <col width="9.08984375" customWidth="1" style="237" min="10245" max="10443"/>
     <col width="1.6328125" customWidth="1" style="237" min="10444" max="10494"/>
     <col width="2.453125" customWidth="1" style="237" min="10495" max="10495"/>
     <col width="3.36328125" customWidth="1" style="237" min="10496" max="10496"/>
-    <col hidden="1" style="237" min="10497" max="10498"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="10497" max="10498"/>
     <col width="3.453125" customWidth="1" style="237" min="10499" max="10499"/>
     <col width="1.6328125" customWidth="1" style="237" min="10500" max="10500"/>
     <col width="9.08984375" customWidth="1" style="237" min="10501" max="10699"/>
     <col width="1.6328125" customWidth="1" style="237" min="10700" max="10750"/>
     <col width="2.453125" customWidth="1" style="237" min="10751" max="10751"/>
     <col width="3.36328125" customWidth="1" style="237" min="10752" max="10752"/>
-    <col hidden="1" style="237" min="10753" max="10754"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="10753" max="10754"/>
     <col width="3.453125" customWidth="1" style="237" min="10755" max="10755"/>
     <col width="1.6328125" customWidth="1" style="237" min="10756" max="10756"/>
     <col width="9.08984375" customWidth="1" style="237" min="10757" max="10955"/>
     <col width="1.6328125" customWidth="1" style="237" min="10956" max="11006"/>
     <col width="2.453125" customWidth="1" style="237" min="11007" max="11007"/>
     <col width="3.36328125" customWidth="1" style="237" min="11008" max="11008"/>
-    <col hidden="1" style="237" min="11009" max="11010"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="11009" max="11010"/>
     <col width="3.453125" customWidth="1" style="237" min="11011" max="11011"/>
     <col width="1.6328125" customWidth="1" style="237" min="11012" max="11012"/>
     <col width="9.08984375" customWidth="1" style="237" min="11013" max="11211"/>
     <col width="1.6328125" customWidth="1" style="237" min="11212" max="11262"/>
     <col width="2.453125" customWidth="1" style="237" min="11263" max="11263"/>
     <col width="3.36328125" customWidth="1" style="237" min="11264" max="11264"/>
-    <col hidden="1" style="237" min="11265" max="11266"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="11265" max="11266"/>
     <col width="3.453125" customWidth="1" style="237" min="11267" max="11267"/>
     <col width="1.6328125" customWidth="1" style="237" min="11268" max="11268"/>
     <col width="9.08984375" customWidth="1" style="237" min="11269" max="11467"/>
     <col width="1.6328125" customWidth="1" style="237" min="11468" max="11518"/>
     <col width="2.453125" customWidth="1" style="237" min="11519" max="11519"/>
     <col width="3.36328125" customWidth="1" style="237" min="11520" max="11520"/>
-    <col hidden="1" style="237" min="11521" max="11522"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="11521" max="11522"/>
     <col width="3.453125" customWidth="1" style="237" min="11523" max="11523"/>
     <col width="1.6328125" customWidth="1" style="237" min="11524" max="11524"/>
     <col width="9.08984375" customWidth="1" style="237" min="11525" max="11723"/>
     <col width="1.6328125" customWidth="1" style="237" min="11724" max="11774"/>
     <col width="2.453125" customWidth="1" style="237" min="11775" max="11775"/>
     <col width="3.36328125" customWidth="1" style="237" min="11776" max="11776"/>
-    <col hidden="1" style="237" min="11777" max="11778"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="11777" max="11778"/>
     <col width="3.453125" customWidth="1" style="237" min="11779" max="11779"/>
     <col width="1.6328125" customWidth="1" style="237" min="11780" max="11780"/>
     <col width="9.08984375" customWidth="1" style="237" min="11781" max="11979"/>
     <col width="1.6328125" customWidth="1" style="237" min="11980" max="12030"/>
     <col width="2.453125" customWidth="1" style="237" min="12031" max="12031"/>
     <col width="3.36328125" customWidth="1" style="237" min="12032" max="12032"/>
-    <col hidden="1" style="237" min="12033" max="12034"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="12033" max="12034"/>
     <col width="3.453125" customWidth="1" style="237" min="12035" max="12035"/>
     <col width="1.6328125" customWidth="1" style="237" min="12036" max="12036"/>
     <col width="9.08984375" customWidth="1" style="237" min="12037" max="12235"/>
     <col width="1.6328125" customWidth="1" style="237" min="12236" max="12286"/>
     <col width="2.453125" customWidth="1" style="237" min="12287" max="12287"/>
     <col width="3.36328125" customWidth="1" style="237" min="12288" max="12288"/>
-    <col hidden="1" style="237" min="12289" max="12290"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="12289" max="12290"/>
     <col width="3.453125" customWidth="1" style="237" min="12291" max="12291"/>
     <col width="1.6328125" customWidth="1" style="237" min="12292" max="12292"/>
     <col width="9.08984375" customWidth="1" style="237" min="12293" max="12491"/>
     <col width="1.6328125" customWidth="1" style="237" min="12492" max="12542"/>
     <col width="2.453125" customWidth="1" style="237" min="12543" max="12543"/>
     <col width="3.36328125" customWidth="1" style="237" min="12544" max="12544"/>
-    <col hidden="1" style="237" min="12545" max="12546"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="12545" max="12546"/>
     <col width="3.453125" customWidth="1" style="237" min="12547" max="12547"/>
     <col width="1.6328125" customWidth="1" style="237" min="12548" max="12548"/>
     <col width="9.08984375" customWidth="1" style="237" min="12549" max="12747"/>
     <col width="1.6328125" customWidth="1" style="237" min="12748" max="12798"/>
     <col width="2.453125" customWidth="1" style="237" min="12799" max="12799"/>
     <col width="3.36328125" customWidth="1" style="237" min="12800" max="12800"/>
-    <col hidden="1" style="237" min="12801" max="12802"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="12801" max="12802"/>
     <col width="3.453125" customWidth="1" style="237" min="12803" max="12803"/>
     <col width="1.6328125" customWidth="1" style="237" min="12804" max="12804"/>
     <col width="9.08984375" customWidth="1" style="237" min="12805" max="13003"/>
     <col width="1.6328125" customWidth="1" style="237" min="13004" max="13054"/>
     <col width="2.453125" customWidth="1" style="237" min="13055" max="13055"/>
     <col width="3.36328125" customWidth="1" style="237" min="13056" max="13056"/>
-    <col hidden="1" style="237" min="13057" max="13058"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="13057" max="13058"/>
     <col width="3.453125" customWidth="1" style="237" min="13059" max="13059"/>
     <col width="1.6328125" customWidth="1" style="237" min="13060" max="13060"/>
     <col width="9.08984375" customWidth="1" style="237" min="13061" max="13259"/>
     <col width="1.6328125" customWidth="1" style="237" min="13260" max="13310"/>
     <col width="2.453125" customWidth="1" style="237" min="13311" max="13311"/>
     <col width="3.36328125" customWidth="1" style="237" min="13312" max="13312"/>
-    <col hidden="1" style="237" min="13313" max="13314"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="13313" max="13314"/>
     <col width="3.453125" customWidth="1" style="237" min="13315" max="13315"/>
     <col width="1.6328125" customWidth="1" style="237" min="13316" max="13316"/>
     <col width="9.08984375" customWidth="1" style="237" min="13317" max="13515"/>
     <col width="1.6328125" customWidth="1" style="237" min="13516" max="13566"/>
     <col width="2.453125" customWidth="1" style="237" min="13567" max="13567"/>
     <col width="3.36328125" customWidth="1" style="237" min="13568" max="13568"/>
-    <col hidden="1" style="237" min="13569" max="13570"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="13569" max="13570"/>
     <col width="3.453125" customWidth="1" style="237" min="13571" max="13571"/>
     <col width="1.6328125" customWidth="1" style="237" min="13572" max="13572"/>
     <col width="9.08984375" customWidth="1" style="237" min="13573" max="13771"/>
     <col width="1.6328125" customWidth="1" style="237" min="13772" max="13822"/>
     <col width="2.453125" customWidth="1" style="237" min="13823" max="13823"/>
     <col width="3.36328125" customWidth="1" style="237" min="13824" max="13824"/>
-    <col hidden="1" style="237" min="13825" max="13826"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="13825" max="13826"/>
     <col width="3.453125" customWidth="1" style="237" min="13827" max="13827"/>
     <col width="1.6328125" customWidth="1" style="237" min="13828" max="13828"/>
     <col width="9.08984375" customWidth="1" style="237" min="13829" max="14027"/>
     <col width="1.6328125" customWidth="1" style="237" min="14028" max="14078"/>
     <col width="2.453125" customWidth="1" style="237" min="14079" max="14079"/>
     <col width="3.36328125" customWidth="1" style="237" min="14080" max="14080"/>
-    <col hidden="1" style="237" min="14081" max="14082"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="14081" max="14082"/>
     <col width="3.453125" customWidth="1" style="237" min="14083" max="14083"/>
     <col width="1.6328125" customWidth="1" style="237" min="14084" max="14084"/>
     <col width="9.08984375" customWidth="1" style="237" min="14085" max="14283"/>
     <col width="1.6328125" customWidth="1" style="237" min="14284" max="14334"/>
     <col width="2.453125" customWidth="1" style="237" min="14335" max="14335"/>
     <col width="3.36328125" customWidth="1" style="237" min="14336" max="14336"/>
-    <col hidden="1" style="237" min="14337" max="14338"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="14337" max="14338"/>
     <col width="3.453125" customWidth="1" style="237" min="14339" max="14339"/>
     <col width="1.6328125" customWidth="1" style="237" min="14340" max="14340"/>
     <col width="9.08984375" customWidth="1" style="237" min="14341" max="14539"/>
     <col width="1.6328125" customWidth="1" style="237" min="14540" max="14590"/>
     <col width="2.453125" customWidth="1" style="237" min="14591" max="14591"/>
     <col width="3.36328125" customWidth="1" style="237" min="14592" max="14592"/>
-    <col hidden="1" style="237" min="14593" max="14594"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="14593" max="14594"/>
     <col width="3.453125" customWidth="1" style="237" min="14595" max="14595"/>
     <col width="1.6328125" customWidth="1" style="237" min="14596" max="14596"/>
     <col width="9.08984375" customWidth="1" style="237" min="14597" max="14795"/>
     <col width="1.6328125" customWidth="1" style="237" min="14796" max="14846"/>
     <col width="2.453125" customWidth="1" style="237" min="14847" max="14847"/>
     <col width="3.36328125" customWidth="1" style="237" min="14848" max="14848"/>
-    <col hidden="1" style="237" min="14849" max="14850"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="14849" max="14850"/>
     <col width="3.453125" customWidth="1" style="237" min="14851" max="14851"/>
     <col width="1.6328125" customWidth="1" style="237" min="14852" max="14852"/>
     <col width="9.08984375" customWidth="1" style="237" min="14853" max="15051"/>
     <col width="1.6328125" customWidth="1" style="237" min="15052" max="15102"/>
     <col width="2.453125" customWidth="1" style="237" min="15103" max="15103"/>
     <col width="3.36328125" customWidth="1" style="237" min="15104" max="15104"/>
-    <col hidden="1" style="237" min="15105" max="15106"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="15105" max="15106"/>
     <col width="3.453125" customWidth="1" style="237" min="15107" max="15107"/>
     <col width="1.6328125" customWidth="1" style="237" min="15108" max="15108"/>
     <col width="9.08984375" customWidth="1" style="237" min="15109" max="15307"/>
     <col width="1.6328125" customWidth="1" style="237" min="15308" max="15358"/>
     <col width="2.453125" customWidth="1" style="237" min="15359" max="15359"/>
     <col width="3.36328125" customWidth="1" style="237" min="15360" max="15360"/>
-    <col hidden="1" style="237" min="15361" max="15362"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="15361" max="15362"/>
     <col width="3.453125" customWidth="1" style="237" min="15363" max="15363"/>
     <col width="1.6328125" customWidth="1" style="237" min="15364" max="15364"/>
     <col width="9.08984375" customWidth="1" style="237" min="15365" max="15563"/>
     <col width="1.6328125" customWidth="1" style="237" min="15564" max="15614"/>
     <col width="2.453125" customWidth="1" style="237" min="15615" max="15615"/>
     <col width="3.36328125" customWidth="1" style="237" min="15616" max="15616"/>
-    <col hidden="1" style="237" min="15617" max="15618"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="15617" max="15618"/>
     <col width="3.453125" customWidth="1" style="237" min="15619" max="15619"/>
     <col width="1.6328125" customWidth="1" style="237" min="15620" max="15620"/>
     <col width="9.08984375" customWidth="1" style="237" min="15621" max="15819"/>
     <col width="1.6328125" customWidth="1" style="237" min="15820" max="15870"/>
     <col width="2.453125" customWidth="1" style="237" min="15871" max="15871"/>
     <col width="3.36328125" customWidth="1" style="237" min="15872" max="15872"/>
-    <col hidden="1" style="237" min="15873" max="15874"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="15873" max="15874"/>
     <col width="3.453125" customWidth="1" style="237" min="15875" max="15875"/>
     <col width="1.6328125" customWidth="1" style="237" min="15876" max="15876"/>
     <col width="9.08984375" customWidth="1" style="237" min="15877" max="16075"/>
     <col width="1.6328125" customWidth="1" style="237" min="16076" max="16126"/>
     <col width="2.453125" customWidth="1" style="237" min="16127" max="16127"/>
     <col width="3.36328125" customWidth="1" style="237" min="16128" max="16128"/>
-    <col hidden="1" style="237" min="16129" max="16130"/>
+    <col hidden="1" width="13" customWidth="1" style="237" min="16129" max="16130"/>
     <col width="3.453125" customWidth="1" style="237" min="16131" max="16131"/>
     <col width="1.6328125" customWidth="1" style="237" min="16132" max="16132"/>
     <col width="9.08984375" customWidth="1" style="237" min="16133" max="16384"/>
@@ -5014,8 +5014,6 @@
     <row r="17">
       <c r="A17" s="258" t="n"/>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="99" t="n"/>
       <c r="B20" s="99" t="n"/>
@@ -5175,8 +5173,6 @@
     <row r="27" ht="15.75" customHeight="1" s="191">
       <c r="A27" s="258" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="99" t="n"/>
       <c r="C30" s="99" t="n"/>
@@ -5653,17 +5649,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A46:BC46"/>
-    <mergeCell ref="AW1:BC1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="K4:Z4"/>
-    <mergeCell ref="K3:Z3"/>
-    <mergeCell ref="AW2:BC2"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:BC46"/>
     <mergeCell ref="K1:Z1"/>
+    <mergeCell ref="AW1:BC1"/>
+    <mergeCell ref="K4:Z4"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="K3:Z3"/>
+    <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="AW2:BC2"/>
     <mergeCell ref="K2:Z2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
